--- a/data/trans_orig/IP16B02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B02-Provincia-trans_orig.xlsx
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>9090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,21%</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>650</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,24%</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2077</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3629</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>8100</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2735</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>234</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3242</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>56,22%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>6401</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14616</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20550</t>
+          <t>20451</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>4530</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4310</t>
+          <t>4284</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>833</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>7223</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>33,93%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2509</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7132</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13436</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18237</t>
+          <t>18231</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>17350</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1885</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>684</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5613</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3539</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>10582</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27316</t>
+          <t>27806</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>36076</t>
+          <t>36010</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>46984</t>
+          <t>48201</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>55411</t>
+          <t>55538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>78912</t>
+          <t>78049</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89573</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4531</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>12801</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,12 +3604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11741</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9759</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13391</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4292</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14027</t>
+          <t>14034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12507</t>
+          <t>12279</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>16806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23796</t>
+          <t>23729</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>625</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4924</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -4776,7 +4776,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15305</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20004</t>
+          <t>19988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>70,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>691</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>29,44%</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5479</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14527</t>
+          <t>14508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,67%</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5237,7 +5237,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4044</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>6252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11457</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16111</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,43%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8606</t>
+          <t>8353</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>9315</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>75,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -5923,7 +5923,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6738</t>
+          <t>6199</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12330</t>
+          <t>12172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12721</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>18356</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>90,36%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1405</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6997</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1448</t>
+          <t>1957</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5794</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9835</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9761</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>15499</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>542</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>572</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4684</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6995</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>57235</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>68588</t>
+          <t>68961</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,48%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59559</t>
+          <t>59379</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>69537</t>
+          <t>69492</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>121270</t>
+          <t>120894</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>136264</t>
+          <t>135732</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>9750</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>21660</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15194</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17552</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>32014</t>
+          <t>32390</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>3216</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>6848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10251</t>
+          <t>10008</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15539</t>
+          <t>15583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>561</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>4193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>40,43%</t>
         </is>
       </c>
     </row>
@@ -7721,7 +7721,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>16563</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3308</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8099,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>2731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2835</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3629</t>
+          <t>3783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>58,07%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9590</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>19265</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25082</t>
+          <t>25148</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,63%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>804</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3425</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8200</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7644</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14043</t>
+          <t>14204</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2630</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>52,11%</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -9849,7 +9849,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>17853</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9982,7 +9982,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>45684</t>
+          <t>45988</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>55696</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>49505</t>
+          <t>49702</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>91907</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>103806</t>
+          <t>103862</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,38%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16291</t>
+          <t>15987</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2174</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>9199</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>21747</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
